--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/SOUTH_DAKOTA_2020.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/SOUTH_DAKOTA_2020.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Chilón</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Santa Isabel</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -667,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Total</t>
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -726,7 +811,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -742,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -825,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -840,7 +955,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -856,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -869,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -882,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -897,12 +1027,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C38">
@@ -913,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -926,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C40">
@@ -939,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>León</t>
@@ -952,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Purísima del Rincón</t>
+          <t>Purísima Del Rincón</t>
         </is>
       </c>
       <c r="C42">
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -978,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -1016,7 +1176,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C46">
@@ -1027,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1040,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -1053,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -1066,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C50">
@@ -1079,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C51">
@@ -1092,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C52">
@@ -1105,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -1118,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1127,7 +1327,7 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>0.09803921568627451</v>
+        <v>0.09803921568627452</v>
       </c>
     </row>
     <row r="55">
@@ -1149,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1180,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -1193,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -1206,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1219,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -1232,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -1245,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C63">
@@ -1258,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C64">
@@ -1271,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C65">
@@ -1284,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -1297,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1328,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Coalcomán de Vázquez Pallares</t>
+          <t>Coalcomán De Vázquez Pallares</t>
         </is>
       </c>
       <c r="C69">
@@ -1341,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -1354,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1367,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -1380,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1393,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Nuevo Urecho</t>
@@ -1406,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -1419,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1450,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -1463,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -1476,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1507,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -1520,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1540,7 +1860,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mier y Noriega</t>
+          <t>Mier Y Noriega</t>
         </is>
       </c>
       <c r="C84">
@@ -1551,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C85">
@@ -1564,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1595,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>San Agustín Loxicha</t>
@@ -1608,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>San Jerónimo Sosola</t>
@@ -1621,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>San Lorenzo Texmelúcan</t>
@@ -1634,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Zapotitlán del Río</t>
+          <t>Zapotitlán Del Río</t>
         </is>
       </c>
       <c r="C91">
@@ -1647,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1678,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -1691,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1704,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -1717,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Soltepec</t>
@@ -1730,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -1743,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -1756,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1776,7 +2166,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C101">
@@ -1787,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -1800,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -1813,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C104">
@@ -1826,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1857,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -1870,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Elota</t>
@@ -1883,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -1896,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1927,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -1940,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Huatabampo</t>
@@ -1953,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1984,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2015,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2046,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -2059,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Espinal</t>
@@ -2072,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -2085,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C123">
@@ -2098,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -2111,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -2124,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -2137,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -2150,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2170,7 +2670,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jiménez del Teul</t>
+          <t>Jiménez Del Teul</t>
         </is>
       </c>
       <c r="C129">
@@ -2181,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -2194,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C131">
@@ -2207,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2230,41 +2745,6 @@
       </c>
       <c r="D133">
         <v>1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 497,795</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Octubre de 2021</t>
-        </is>
       </c>
     </row>
   </sheetData>
